--- a/kvcache/unified_kv_memory/关键过程件/V2.3.1关键文档联动刷新_20260809/统一异构KVCache存储池_全量需求树_V2.3.1_SR项目贡献补充版.xlsx
+++ b/kvcache/unified_kv_memory/关键过程件/V2.3.1关键文档联动刷新_20260809/统一异构KVCache存储池_全量需求树_V2.3.1_SR项目贡献补充版.xlsx
@@ -1300,7 +1300,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="11"/>
   </cols>
@@ -1577,7 +1577,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2000,7 +2000,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -2640,7 +2640,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4354,7 +4354,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Y22" s="36" t="inlineStr">
         <is>
-          <t>模块功能闭包｜按实际路径形成完整性证据、RAS 故障映射和阻断规则；为第一方问题归因、错误消费防护和跨版本认证提供可审计依据。</t>
+          <t>模块功能闭包｜按实际路径形成完整性证据、RAS 故障映射和阻断规则；为原厂系统问题归因、错误消费防护和跨版本认证提供可审计依据。</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Y37" s="36" t="inlineStr">
         <is>
-          <t>模块功能闭包｜交付链路追踪、回退分析和 KV 检查（KVInspect）工具；缩短跨框架、传输、驱动与硬件的问题定位路径，形成第一方责任闭环。</t>
+          <t>模块功能闭包｜交付链路追踪、回退分析和 KV 检查（KVInspect）工具；缩短跨框架、传输、驱动与硬件的问题定位路径，形成原厂软硬件协同系统责任闭环。</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T207"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -27917,7 +27917,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P153"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -39989,7 +39989,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -41829,7 +41829,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -43915,7 +43915,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L271"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -60097,7 +60097,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
